--- a/evals/unit_tests_comparative/test03_attention_fused_vs_unfused/analysis_output_ref/perf_report_trace2.xlsx
+++ b/evals/unit_tests_comparative/test03_attention_fused_vs_unfused/analysis_output_ref/perf_report_trace2.xlsx
@@ -11,8 +11,9 @@
     <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="unified_perf_callstacks" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="unified_perf_summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GEMM" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1123,15 +1124,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>row_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>op category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>call_stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aten::bmm =&gt; aten::bmm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::softmax</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>aten::softmax =&gt; aten::softmax</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>op category</t>
@@ -1369,10 +1446,15 @@
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
+          <t>trunc_call_stack</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
           <t>Percentage (%)</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Cumulative Percentage (%)</t>
         </is>
@@ -1527,7 +1609,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[{'name': 'volta_h16gemm_&lt;BF16,BF16,float&gt;_tt_v1', 'stream': 7, 'gpu_op_uid': 6, 'count': 2, 'total_duration_us': np.float64(520.0), 'gpu_op_uids': [6, 16], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(250.0), 'min_duration_us': np.float64(10.0), 'max_duration_us': np.float64(510.0)}]</t>
+          <t>[{'name': 'volta_h16gemm_&lt;BF16,BF16,float&gt;_tt_v1', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(520.0), 'gpu_op_uids': [6, 16], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(250.0), 'min_duration_us': np.float64(10.0), 'max_duration_us': np.float64(510.0)}]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -1543,10 +1625,15 @@
       <c r="AV2" t="b">
         <v>1</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>aten::bmm =&gt; aten::bmm</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>66.66666666666666</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>66.66666666666666</v>
       </c>
     </row>
@@ -1649,7 +1736,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[{'name': 'softmax_warp_forward&lt;float, float, float, 4, true&gt;', 'stream': 7, 'gpu_op_uid': 11, 'count': 1, 'total_duration_us': np.float64(260.0), 'gpu_op_uids': [11], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(260.0), 'max_duration_us': np.float64(260.0)}]</t>
+          <t>[{'name': 'softmax_warp_forward&lt;float, float, float, 4, true&gt;', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(260.0), 'gpu_op_uids': [11], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(260.0), 'max_duration_us': np.float64(260.0)}]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1661,10 +1748,15 @@
       <c r="AV3" t="b">
         <v>0</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>aten::softmax =&gt; aten::softmax</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>99.99999999999999</v>
       </c>
     </row>
@@ -1673,7 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2059,7 +2151,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[{'name': 'volta_h16gemm_&lt;BF16,BF16,float&gt;_tt_v1', 'stream': 7, 'gpu_op_uid': 6, 'count': 2, 'total_duration_us': np.float64(520.0), 'gpu_op_uids': [6, 16], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(250.0), 'min_duration_us': np.float64(10.0), 'max_duration_us': np.float64(510.0)}]</t>
+          <t>[{'name': 'volta_h16gemm_&lt;BF16,BF16,float&gt;_tt_v1', 'stream': 7, 'count': 2, 'total_duration_us': np.float64(520.0), 'gpu_op_uids': [6, 16], 'mean_duration_us': np.float64(260.0), 'median_duration_us': np.float64(260.0), 'std_dev_duration_us': np.float64(250.0), 'min_duration_us': np.float64(10.0), 'max_duration_us': np.float64(510.0)}]</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
